--- a/templates/supplier-template.xlsx
+++ b/templates/supplier-template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>nama</t>
   </si>
@@ -70,10 +70,37 @@
     <t>Pasar Baa</t>
   </si>
   <si>
-    <t>mie snack</t>
+    <t>mie minuman snack</t>
   </si>
   <si>
     <t>bisa COD</t>
+  </si>
+  <si>
+    <t>Agen Rokok Rote</t>
+  </si>
+  <si>
+    <t>0821xxxxxxx</t>
+  </si>
+  <si>
+    <t>Ba'a</t>
+  </si>
+  <si>
+    <t>rokok</t>
+  </si>
+  <si>
+    <t>harga ikut pita cukai</t>
+  </si>
+  <si>
+    <t>Pangkalan Gas Baa</t>
+  </si>
+  <si>
+    <t>0838xxxxxxx</t>
+  </si>
+  <si>
+    <t>gas LPG 3kg</t>
+  </si>
+  <si>
+    <t>ambil sendiri, antri pagi</t>
   </si>
 </sst>
 </file>
@@ -459,6 +486,40 @@
         <v>19</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/templates/supplier-template.xlsx
+++ b/templates/supplier-template.xlsx
@@ -107,7 +107,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,18 +117,34 @@
     <font>
       <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B4F72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -136,14 +152,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFC9CA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFC9CA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFC9CA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFC9CA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,10 +451,14 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="5" min="1" width="18"/>
+    <col customWidth="true" max="1" min="1" width="24"/>
+    <col customWidth="true" max="2" min="2" width="18"/>
+    <col customWidth="true" max="3" min="3" width="30"/>
+    <col customWidth="true" max="4" min="4" width="28"/>
+    <col customWidth="true" max="5" min="5" width="38"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,89 +476,299 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>28</v>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
     </row>
   </sheetData>
 </worksheet>

--- a/templates/supplier-template.xlsx
+++ b/templates/supplier-template.xlsx
@@ -8,106 +8,199 @@
   </bookViews>
   <sheets>
     <sheet name="Supplier" sheetId="1" r:id="rId1"/>
+    <sheet name="Petunjuk" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Supplier'!$A$1:$E$36</definedName>
+  </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Kios Cerdas</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <t>⚠️ WAJIB DIISI
+Nama supplier/pemasok.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>ℹ️ Opsional
+Nomor kontak/telepon supplier.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <t>ℹ️ Opsional
+Alamat supplier.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <t>ℹ️ Opsional
+Jenis produk utama yang disuplai.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <t>ℹ️ Opsional
+Catatan tambahan (MOQ, lead time, dll).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+  <si>
+    <t>nama *</t>
+  </si>
+  <si>
+    <t>kontak</t>
+  </si>
+  <si>
+    <t>alamat</t>
+  </si>
+  <si>
+    <t>produk_utama</t>
+  </si>
+  <si>
+    <t>catatan</t>
+  </si>
+  <si>
+    <t>UD Maju</t>
+  </si>
+  <si>
+    <t>0812xxxxxxx</t>
+  </si>
+  <si>
+    <t>Baa Rote Ndao</t>
+  </si>
+  <si>
+    <t>beras gula minyak</t>
+  </si>
+  <si>
+    <t>MOQ 10 karung; lead time 2 hari</t>
+  </si>
+  <si>
+    <t>Distributor Kupang</t>
+  </si>
+  <si>
+    <t>0813xxxxxxx</t>
+  </si>
+  <si>
+    <t>Kupang NTT</t>
+  </si>
+  <si>
+    <t>sembako</t>
+  </si>
+  <si>
+    <t>kirim tiap Senin</t>
+  </si>
+  <si>
+    <t>Grosir Baa</t>
+  </si>
+  <si>
+    <t>0852xxxxxxx</t>
+  </si>
+  <si>
+    <t>Pasar Baa</t>
+  </si>
+  <si>
+    <t>mie minuman snack</t>
+  </si>
+  <si>
+    <t>bisa COD</t>
+  </si>
+  <si>
+    <t>Agen Rokok Rote</t>
+  </si>
+  <si>
+    <t>0821xxxxxxx</t>
+  </si>
+  <si>
+    <t>Ba'a</t>
+  </si>
+  <si>
+    <t>rokok</t>
+  </si>
+  <si>
+    <t>harga ikut pita cukai</t>
+  </si>
+  <si>
+    <t>Pangkalan Gas Baa</t>
+  </si>
+  <si>
+    <t>0838xxxxxxx</t>
+  </si>
+  <si>
+    <t>gas LPG 3kg</t>
+  </si>
+  <si>
+    <t>ambil sendiri, antri pagi</t>
+  </si>
+  <si>
+    <t>Panduan Pengisian Template</t>
+  </si>
+  <si>
+    <t>Template ini untuk mengimport data supplier ke Kios Cerdas.
+Isi kolom sesuai panduan, lalu simpan dan import via bot Telegram.</t>
+  </si>
+  <si>
+    <t>Kolom</t>
+  </si>
+  <si>
+    <t>Wajib?</t>
+  </si>
+  <si>
+    <t>Contoh</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>Validasi</t>
+  </si>
   <si>
     <t>nama</t>
   </si>
   <si>
-    <t>kontak</t>
-  </si>
-  <si>
-    <t>alamat</t>
-  </si>
-  <si>
-    <t>produk_utama</t>
-  </si>
-  <si>
-    <t>catatan</t>
-  </si>
-  <si>
-    <t>UD Maju</t>
-  </si>
-  <si>
-    <t>0812xxxxxxx</t>
-  </si>
-  <si>
-    <t>Baa Rote Ndao</t>
-  </si>
-  <si>
-    <t>beras gula minyak</t>
-  </si>
-  <si>
-    <t>MOQ 10 karung; lead time 2 hari</t>
-  </si>
-  <si>
-    <t>Distributor Kupang</t>
-  </si>
-  <si>
-    <t>0813xxxxxxx</t>
-  </si>
-  <si>
-    <t>Kupang NTT</t>
-  </si>
-  <si>
-    <t>sembako</t>
-  </si>
-  <si>
-    <t>kirim tiap Senin</t>
-  </si>
-  <si>
-    <t>Grosir Baa</t>
-  </si>
-  <si>
-    <t>0852xxxxxxx</t>
-  </si>
-  <si>
-    <t>Pasar Baa</t>
-  </si>
-  <si>
-    <t>mie minuman snack</t>
-  </si>
-  <si>
-    <t>bisa COD</t>
-  </si>
-  <si>
-    <t>Agen Rokok Rote</t>
-  </si>
-  <si>
-    <t>0821xxxxxxx</t>
-  </si>
-  <si>
-    <t>Ba'a</t>
-  </si>
-  <si>
-    <t>rokok</t>
-  </si>
-  <si>
-    <t>harga ikut pita cukai</t>
-  </si>
-  <si>
-    <t>Pangkalan Gas Baa</t>
-  </si>
-  <si>
-    <t>0838xxxxxxx</t>
-  </si>
-  <si>
-    <t>gas LPG 3kg</t>
-  </si>
-  <si>
-    <t>ambil sendiri, antri pagi</t>
+    <t>WAJIB</t>
+  </si>
+  <si>
+    <t>Nama supplier/pemasok.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Opsional</t>
+  </si>
+  <si>
+    <t>Nomor kontak/telepon supplier.</t>
+  </si>
+  <si>
+    <t>Alamat supplier.</t>
+  </si>
+  <si>
+    <t>Jenis produk utama yang disuplai.</t>
+  </si>
+  <si>
+    <t>Catatan tambahan (MOQ, lead time, dll).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,11 +211,34 @@
       <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF2D3436"/>
       <sz val="11"/>
     </font>
     <font>
       <family val="2"/>
-      <color/>
+      <b val="1"/>
+      <color rgb="FF0D7C66"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF555555"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFC0392B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -135,12 +251,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B4F72"/>
+        <fgColor rgb="FF0D7C66"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6EAF8"/>
+        <fgColor rgb="FFF0F7F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,23 +270,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -180,6 +296,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,6 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -458,7 +590,7 @@
     <col customWidth="true" max="5" min="5" width="38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="true">
+    <row r="1" ht="32" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -771,5 +903,138 @@
       <c r="E36" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="$A$1:$E$36"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="22"/>
+    <col customWidth="true" max="2" min="2" width="12"/>
+    <col customWidth="true" max="3" min="3" width="40"/>
+    <col customWidth="true" max="4" min="4" width="46"/>
+    <col customWidth="true" max="5" min="5" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="true">
+      <c r="A1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="true">
+      <c r="A2" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="true">
+      <c r="A5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="true">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="true">
+      <c r="A7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="true">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="true">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
 </worksheet>
 </file>